--- a/output/yearly_population_iteration_1_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_1_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6677</v>
+        <v>4016</v>
       </c>
       <c r="C2" t="n">
-        <v>3689</v>
+        <v>11168</v>
       </c>
       <c r="D2" t="n">
-        <v>26333</v>
+        <v>33372</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4080</v>
+        <v>2860</v>
       </c>
       <c r="C3" t="n">
-        <v>3969</v>
+        <v>5594</v>
       </c>
       <c r="D3" t="n">
-        <v>15507</v>
+        <v>14602</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3265</v>
+        <v>2268</v>
       </c>
       <c r="C4" t="n">
-        <v>5820</v>
+        <v>5979</v>
       </c>
       <c r="D4" t="n">
-        <v>7474</v>
+        <v>9057</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2109</v>
+        <v>1500</v>
       </c>
       <c r="C5" t="n">
-        <v>5522</v>
+        <v>5255</v>
       </c>
       <c r="D5" t="n">
-        <v>2809</v>
+        <v>3966</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1170</v>
+        <v>879</v>
       </c>
       <c r="C6" t="n">
-        <v>3588</v>
+        <v>3134</v>
       </c>
       <c r="D6" t="n">
-        <v>1155</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>542</v>
+        <v>408</v>
       </c>
       <c r="C7" t="n">
-        <v>1681</v>
+        <v>1697</v>
       </c>
       <c r="D7" t="n">
-        <v>655</v>
+        <v>719</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>206</v>
+        <v>154</v>
       </c>
       <c r="C8" t="n">
-        <v>600</v>
+        <v>746</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>257</v>
+        <v>332</v>
       </c>
       <c r="D9" t="n">
         <v>307</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8470</v>
+        <v>5858</v>
       </c>
       <c r="C2" t="n">
-        <v>4388</v>
+        <v>9889</v>
       </c>
       <c r="D2" t="n">
-        <v>26522</v>
+        <v>29971</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4240</v>
+        <v>2754</v>
       </c>
       <c r="C3" t="n">
-        <v>3389</v>
+        <v>7116</v>
       </c>
       <c r="D3" t="n">
-        <v>15937</v>
+        <v>16173</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3094</v>
+        <v>2177</v>
       </c>
       <c r="C4" t="n">
-        <v>4772</v>
+        <v>5673</v>
       </c>
       <c r="D4" t="n">
-        <v>8557</v>
+        <v>9686</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2320</v>
+        <v>1612</v>
       </c>
       <c r="C5" t="n">
-        <v>5544</v>
+        <v>5421</v>
       </c>
       <c r="D5" t="n">
-        <v>3413</v>
+        <v>4589</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1421</v>
+        <v>1038</v>
       </c>
       <c r="C6" t="n">
-        <v>4372</v>
+        <v>4040</v>
       </c>
       <c r="D6" t="n">
-        <v>1393</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>720</v>
+        <v>541</v>
       </c>
       <c r="C7" t="n">
-        <v>2521</v>
+        <v>2299</v>
       </c>
       <c r="D7" t="n">
-        <v>715</v>
+        <v>820</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>304</v>
+        <v>229</v>
       </c>
       <c r="C8" t="n">
-        <v>1049</v>
+        <v>1139</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="C9" t="n">
-        <v>398</v>
+        <v>502</v>
       </c>
       <c r="D9" t="n">
         <v>318</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>255</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9260</v>
+        <v>6232</v>
       </c>
       <c r="C2" t="n">
-        <v>12481</v>
+        <v>11255</v>
       </c>
       <c r="D2" t="n">
-        <v>23778</v>
+        <v>31389</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4850</v>
+        <v>3212</v>
       </c>
       <c r="C3" t="n">
-        <v>3369</v>
+        <v>7385</v>
       </c>
       <c r="D3" t="n">
-        <v>16187</v>
+        <v>16793</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3023</v>
+        <v>2055</v>
       </c>
       <c r="C4" t="n">
-        <v>4029</v>
+        <v>6110</v>
       </c>
       <c r="D4" t="n">
-        <v>9277</v>
+        <v>10232</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2342</v>
+        <v>1635</v>
       </c>
       <c r="C5" t="n">
-        <v>5102</v>
+        <v>5360</v>
       </c>
       <c r="D5" t="n">
-        <v>4049</v>
+        <v>5183</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1616</v>
+        <v>1154</v>
       </c>
       <c r="C6" t="n">
-        <v>4763</v>
+        <v>4561</v>
       </c>
       <c r="D6" t="n">
-        <v>1632</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>892</v>
+        <v>666</v>
       </c>
       <c r="C7" t="n">
-        <v>3239</v>
+        <v>2958</v>
       </c>
       <c r="D7" t="n">
-        <v>800</v>
+        <v>954</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>413</v>
+        <v>305</v>
       </c>
       <c r="C8" t="n">
-        <v>1625</v>
+        <v>1570</v>
       </c>
       <c r="D8" t="n">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>160</v>
+        <v>121</v>
       </c>
       <c r="C9" t="n">
-        <v>636</v>
+        <v>739</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>284</v>
+        <v>339</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8493</v>
+        <v>5703</v>
       </c>
       <c r="C2" t="n">
-        <v>8586</v>
+        <v>7743</v>
       </c>
       <c r="D2" t="n">
-        <v>19799</v>
+        <v>25917</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5633</v>
+        <v>3775</v>
       </c>
       <c r="C3" t="n">
-        <v>6295</v>
+        <v>10872</v>
       </c>
       <c r="D3" t="n">
-        <v>17612</v>
+        <v>18458</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2164</v>
+        <v>1510</v>
       </c>
       <c r="C4" t="n">
-        <v>7102</v>
+        <v>8488</v>
       </c>
       <c r="D4" t="n">
-        <v>8854</v>
+        <v>10261</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1493</v>
+        <v>1066</v>
       </c>
       <c r="C5" t="n">
-        <v>4667</v>
+        <v>4469</v>
       </c>
       <c r="D5" t="n">
-        <v>2687</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>824</v>
+        <v>615</v>
       </c>
       <c r="C6" t="n">
-        <v>3174</v>
+        <v>2898</v>
       </c>
       <c r="D6" t="n">
-        <v>784</v>
+        <v>934</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>381</v>
+        <v>281</v>
       </c>
       <c r="C7" t="n">
-        <v>1592</v>
+        <v>1538</v>
       </c>
       <c r="D7" t="n">
-        <v>473</v>
+        <v>496</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>623</v>
+        <v>724</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>278</v>
+        <v>332</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5329</v>
+        <v>3416</v>
       </c>
       <c r="C2" t="n">
-        <v>3975</v>
+        <v>4325</v>
       </c>
       <c r="D2" t="n">
-        <v>14990</v>
+        <v>18261</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5885</v>
+        <v>3947</v>
       </c>
       <c r="C3" t="n">
-        <v>6645</v>
+        <v>8586</v>
       </c>
       <c r="D3" t="n">
-        <v>16894</v>
+        <v>18586</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3014</v>
+        <v>2071</v>
       </c>
       <c r="C4" t="n">
-        <v>6786</v>
+        <v>9735</v>
       </c>
       <c r="D4" t="n">
-        <v>10100</v>
+        <v>11227</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1661</v>
+        <v>1165</v>
       </c>
       <c r="C5" t="n">
-        <v>5799</v>
+        <v>6211</v>
       </c>
       <c r="D5" t="n">
-        <v>3426</v>
+        <v>4334</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>979</v>
+        <v>727</v>
       </c>
       <c r="C6" t="n">
-        <v>3852</v>
+        <v>3574</v>
       </c>
       <c r="D6" t="n">
-        <v>980</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>359</v>
+        <v>263</v>
       </c>
       <c r="C7" t="n">
-        <v>2165</v>
+        <v>2032</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>876</v>
+        <v>955</v>
       </c>
       <c r="D8" t="n">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>322</v>
+        <v>376</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
         <v>210</v>
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
+        <v>163</v>
+      </c>
+      <c r="D11" t="n">
         <v>165</v>
-      </c>
-      <c r="D11" t="n">
-        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5157</v>
+        <v>2947</v>
       </c>
       <c r="C2" t="n">
-        <v>9457</v>
+        <v>3714</v>
       </c>
       <c r="D2" t="n">
-        <v>21407</v>
+        <v>14889</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4741</v>
+        <v>3131</v>
       </c>
       <c r="C3" t="n">
-        <v>4779</v>
+        <v>5885</v>
       </c>
       <c r="D3" t="n">
-        <v>15619</v>
+        <v>17292</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3672</v>
+        <v>2472</v>
       </c>
       <c r="C4" t="n">
-        <v>6575</v>
+        <v>8980</v>
       </c>
       <c r="D4" t="n">
-        <v>10901</v>
+        <v>12086</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1983</v>
+        <v>1370</v>
       </c>
       <c r="C5" t="n">
-        <v>6142</v>
+        <v>7705</v>
       </c>
       <c r="D5" t="n">
-        <v>4346</v>
+        <v>5261</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1158</v>
+        <v>833</v>
       </c>
       <c r="C6" t="n">
-        <v>4730</v>
+        <v>4739</v>
       </c>
       <c r="D6" t="n">
-        <v>1319</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>534</v>
+        <v>389</v>
       </c>
       <c r="C7" t="n">
-        <v>2912</v>
+        <v>2700</v>
       </c>
       <c r="D7" t="n">
-        <v>575</v>
+        <v>635</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>180</v>
+        <v>134</v>
       </c>
       <c r="C8" t="n">
-        <v>1402</v>
+        <v>1376</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>531</v>
+        <v>598</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
         <v>63</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>35</v>
+      </c>
+      <c r="D16" t="n">
         <v>36</v>
-      </c>
-      <c r="D16" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3080</v>
+        <v>1766</v>
       </c>
       <c r="C2" t="n">
-        <v>4435</v>
+        <v>1779</v>
       </c>
       <c r="D2" t="n">
-        <v>14923</v>
+        <v>10387</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4670</v>
+        <v>2980</v>
       </c>
       <c r="C3" t="n">
-        <v>6205</v>
+        <v>5003</v>
       </c>
       <c r="D3" t="n">
-        <v>15871</v>
+        <v>16654</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4060</v>
+        <v>2718</v>
       </c>
       <c r="C4" t="n">
-        <v>6483</v>
+        <v>8674</v>
       </c>
       <c r="D4" t="n">
-        <v>11542</v>
+        <v>12799</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2065</v>
+        <v>1438</v>
       </c>
       <c r="C5" t="n">
-        <v>7162</v>
+        <v>9115</v>
       </c>
       <c r="D5" t="n">
-        <v>4586</v>
+        <v>5524</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>964</v>
+        <v>690</v>
       </c>
       <c r="C6" t="n">
-        <v>5670</v>
+        <v>5608</v>
       </c>
       <c r="D6" t="n">
-        <v>1291</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>166</v>
+        <v>123</v>
       </c>
       <c r="C7" t="n">
-        <v>2888</v>
+        <v>2703</v>
       </c>
       <c r="D7" t="n">
-        <v>576</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>946</v>
+        <v>1004</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>34</v>
+      </c>
+      <c r="D15" t="n">
         <v>35</v>
-      </c>
-      <c r="D15" t="n">
-        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3865</v>
+        <v>2590</v>
       </c>
       <c r="C2" t="n">
-        <v>6075</v>
+        <v>5489</v>
       </c>
       <c r="D2" t="n">
-        <v>13303</v>
+        <v>15130</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3437</v>
+        <v>2139</v>
       </c>
       <c r="C3" t="n">
-        <v>4811</v>
+        <v>3194</v>
       </c>
       <c r="D3" t="n">
-        <v>14827</v>
+        <v>14842</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3765</v>
+        <v>2470</v>
       </c>
       <c r="C4" t="n">
-        <v>6217</v>
+        <v>6801</v>
       </c>
       <c r="D4" t="n">
-        <v>11856</v>
+        <v>13002</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2542</v>
+        <v>1727</v>
       </c>
       <c r="C5" t="n">
-        <v>6775</v>
+        <v>8818</v>
       </c>
       <c r="D5" t="n">
-        <v>5448</v>
+        <v>6403</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1260</v>
+        <v>883</v>
       </c>
       <c r="C6" t="n">
-        <v>6303</v>
+        <v>7060</v>
       </c>
       <c r="D6" t="n">
-        <v>1717</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>361</v>
+        <v>255</v>
       </c>
       <c r="C7" t="n">
-        <v>4061</v>
+        <v>3893</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>742</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>1668</v>
+        <v>1622</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>479</v>
+        <v>505</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
+        <v>128</v>
+      </c>
+      <c r="D11" t="n">
         <v>133</v>
-      </c>
-      <c r="D11" t="n">
-        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3131,7 +3131,7 @@
         <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2718</v>
+        <v>1675</v>
       </c>
       <c r="C2" t="n">
-        <v>4608</v>
+        <v>3095</v>
       </c>
       <c r="D2" t="n">
-        <v>11100</v>
+        <v>11413</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3132</v>
+        <v>1998</v>
       </c>
       <c r="C3" t="n">
-        <v>4865</v>
+        <v>3741</v>
       </c>
       <c r="D3" t="n">
-        <v>13837</v>
+        <v>14211</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3348</v>
+        <v>2169</v>
       </c>
       <c r="C4" t="n">
-        <v>5640</v>
+        <v>5370</v>
       </c>
       <c r="D4" t="n">
-        <v>12008</v>
+        <v>12961</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2781</v>
+        <v>1867</v>
       </c>
       <c r="C5" t="n">
-        <v>6690</v>
+        <v>8256</v>
       </c>
       <c r="D5" t="n">
-        <v>6125</v>
+        <v>6966</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1496</v>
+        <v>1028</v>
       </c>
       <c r="C6" t="n">
-        <v>6713</v>
+        <v>7882</v>
       </c>
       <c r="D6" t="n">
-        <v>2052</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>325</v>
+        <v>229</v>
       </c>
       <c r="C7" t="n">
-        <v>4887</v>
+        <v>4903</v>
       </c>
       <c r="D7" t="n">
-        <v>758</v>
+        <v>834</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>2213</v>
+        <v>2122</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5142</v>
+        <v>2096</v>
       </c>
       <c r="C2" t="n">
-        <v>4048</v>
+        <v>6956</v>
       </c>
       <c r="D2" t="n">
-        <v>16159</v>
+        <v>13435</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2512</v>
+        <v>1588</v>
       </c>
       <c r="C3" t="n">
-        <v>4274</v>
+        <v>3136</v>
       </c>
       <c r="D3" t="n">
-        <v>12622</v>
+        <v>12965</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2843</v>
+        <v>1833</v>
       </c>
       <c r="C4" t="n">
-        <v>5195</v>
+        <v>4585</v>
       </c>
       <c r="D4" t="n">
-        <v>11906</v>
+        <v>12746</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2742</v>
+        <v>1817</v>
       </c>
       <c r="C5" t="n">
-        <v>6127</v>
+        <v>6948</v>
       </c>
       <c r="D5" t="n">
-        <v>6729</v>
+        <v>7559</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1791</v>
+        <v>1201</v>
       </c>
       <c r="C6" t="n">
-        <v>6647</v>
+        <v>7957</v>
       </c>
       <c r="D6" t="n">
-        <v>2534</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>612</v>
+        <v>426</v>
       </c>
       <c r="C7" t="n">
-        <v>5565</v>
+        <v>5981</v>
       </c>
       <c r="D7" t="n">
-        <v>895</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="C8" t="n">
-        <v>3177</v>
+        <v>3095</v>
       </c>
       <c r="D8" t="n">
-        <v>449</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1107</v>
+        <v>1063</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -3711,7 +3711,7 @@
         <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7394</v>
+        <v>4475</v>
       </c>
       <c r="C2" t="n">
-        <v>1794</v>
+        <v>5577</v>
       </c>
       <c r="D2" t="n">
-        <v>6014</v>
+        <v>23010</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3678</v>
+        <v>1515</v>
       </c>
       <c r="C2" t="n">
-        <v>2331</v>
+        <v>4006</v>
       </c>
       <c r="D2" t="n">
-        <v>11893</v>
+        <v>9995</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3513</v>
+        <v>2114</v>
       </c>
       <c r="C3" t="n">
-        <v>4558</v>
+        <v>4267</v>
       </c>
       <c r="D3" t="n">
-        <v>13951</v>
+        <v>14055</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3959</v>
+        <v>2613</v>
       </c>
       <c r="C4" t="n">
-        <v>7320</v>
+        <v>6903</v>
       </c>
       <c r="D4" t="n">
-        <v>12244</v>
+        <v>13193</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1730</v>
+        <v>1143</v>
       </c>
       <c r="C5" t="n">
-        <v>9210</v>
+        <v>10785</v>
       </c>
       <c r="D5" t="n">
-        <v>6086</v>
+        <v>6923</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>565</v>
+        <v>393</v>
       </c>
       <c r="C6" t="n">
-        <v>6756</v>
+        <v>7342</v>
       </c>
       <c r="D6" t="n">
-        <v>2004</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="C7" t="n">
-        <v>3113</v>
+        <v>3033</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1084</v>
+        <v>1041</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -4319,7 +4319,7 @@
         <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
         <v>62</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7186</v>
+        <v>5874</v>
       </c>
       <c r="C2" t="n">
-        <v>5695</v>
+        <v>5688</v>
       </c>
       <c r="D2" t="n">
-        <v>20153</v>
+        <v>34167</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3140</v>
+        <v>1903</v>
       </c>
       <c r="C3" t="n">
-        <v>918</v>
+        <v>2810</v>
       </c>
       <c r="D3" t="n">
-        <v>1697</v>
+        <v>4505</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5128</v>
+        <v>5021</v>
       </c>
       <c r="C2" t="n">
-        <v>11493</v>
+        <v>6855</v>
       </c>
       <c r="D2" t="n">
-        <v>21845</v>
+        <v>32816</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4242</v>
+        <v>3191</v>
       </c>
       <c r="C3" t="n">
-        <v>3159</v>
+        <v>3827</v>
       </c>
       <c r="D3" t="n">
-        <v>4672</v>
+        <v>9156</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1398</v>
+        <v>861</v>
       </c>
       <c r="C4" t="n">
-        <v>590</v>
+        <v>1691</v>
       </c>
       <c r="D4" t="n">
-        <v>1523</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5098</v>
+        <v>4269</v>
       </c>
       <c r="C2" t="n">
-        <v>7456</v>
+        <v>8037</v>
       </c>
       <c r="D2" t="n">
-        <v>26018</v>
+        <v>29029</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3853</v>
+        <v>3354</v>
       </c>
       <c r="C3" t="n">
-        <v>6668</v>
+        <v>4723</v>
       </c>
       <c r="D3" t="n">
-        <v>7083</v>
+        <v>12282</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2390</v>
+        <v>1720</v>
       </c>
       <c r="C4" t="n">
-        <v>2032</v>
+        <v>2828</v>
       </c>
       <c r="D4" t="n">
-        <v>2081</v>
+        <v>3382</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>634</v>
+        <v>407</v>
       </c>
       <c r="C5" t="n">
-        <v>415</v>
+        <v>1022</v>
       </c>
       <c r="D5" t="n">
-        <v>1200</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5288,7 +5288,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
         <v>115</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7868</v>
+        <v>4326</v>
       </c>
       <c r="C2" t="n">
-        <v>12321</v>
+        <v>9604</v>
       </c>
       <c r="D2" t="n">
-        <v>23598</v>
+        <v>22561</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3656</v>
+        <v>3114</v>
       </c>
       <c r="C3" t="n">
-        <v>6156</v>
+        <v>5576</v>
       </c>
       <c r="D3" t="n">
-        <v>9462</v>
+        <v>13962</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2662</v>
+        <v>2120</v>
       </c>
       <c r="C4" t="n">
-        <v>4462</v>
+        <v>3742</v>
       </c>
       <c r="D4" t="n">
-        <v>2910</v>
+        <v>4902</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1244</v>
+        <v>873</v>
       </c>
       <c r="C5" t="n">
-        <v>1260</v>
+        <v>1936</v>
       </c>
       <c r="D5" t="n">
-        <v>1324</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>335</v>
+        <v>241</v>
       </c>
       <c r="C6" t="n">
-        <v>356</v>
+        <v>660</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5613,10 +5613,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7475</v>
+        <v>5330</v>
       </c>
       <c r="C2" t="n">
-        <v>8075</v>
+        <v>11244</v>
       </c>
       <c r="D2" t="n">
-        <v>34819</v>
+        <v>27385</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4126</v>
+        <v>2695</v>
       </c>
       <c r="C3" t="n">
-        <v>7623</v>
+        <v>6225</v>
       </c>
       <c r="D3" t="n">
-        <v>10297</v>
+        <v>13442</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1949</v>
+        <v>1625</v>
       </c>
       <c r="C4" t="n">
-        <v>4386</v>
+        <v>3845</v>
       </c>
       <c r="D4" t="n">
-        <v>3505</v>
+        <v>5588</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1027</v>
+        <v>769</v>
       </c>
       <c r="C5" t="n">
-        <v>2166</v>
+        <v>2099</v>
       </c>
       <c r="D5" t="n">
-        <v>1251</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>370</v>
+        <v>261</v>
       </c>
       <c r="C6" t="n">
-        <v>546</v>
+        <v>864</v>
       </c>
       <c r="D6" t="n">
-        <v>769</v>
+        <v>819</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>224</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5980</v>
+        <v>4299</v>
       </c>
       <c r="C2" t="n">
-        <v>6136</v>
+        <v>5335</v>
       </c>
       <c r="D2" t="n">
-        <v>25313</v>
+        <v>21908</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4821</v>
+        <v>3319</v>
       </c>
       <c r="C3" t="n">
-        <v>6777</v>
+        <v>7937</v>
       </c>
       <c r="D3" t="n">
-        <v>13658</v>
+        <v>14795</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2676</v>
+        <v>1886</v>
       </c>
       <c r="C4" t="n">
-        <v>6252</v>
+        <v>5144</v>
       </c>
       <c r="D4" t="n">
-        <v>4734</v>
+        <v>6947</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1330</v>
+        <v>1054</v>
       </c>
       <c r="C5" t="n">
-        <v>3420</v>
+        <v>3077</v>
       </c>
       <c r="D5" t="n">
-        <v>1667</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>642</v>
+        <v>475</v>
       </c>
       <c r="C6" t="n">
-        <v>1456</v>
+        <v>1552</v>
       </c>
       <c r="D6" t="n">
-        <v>850</v>
+        <v>979</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>215</v>
+        <v>156</v>
       </c>
       <c r="C7" t="n">
-        <v>401</v>
+        <v>624</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>274</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6165,10 +6165,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D9" t="n">
         <v>283</v>
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6255,7 +6255,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5559</v>
+        <v>3882</v>
       </c>
       <c r="C2" t="n">
-        <v>3485</v>
+        <v>7150</v>
       </c>
       <c r="D2" t="n">
-        <v>28208</v>
+        <v>20136</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4438</v>
+        <v>3121</v>
       </c>
       <c r="C3" t="n">
-        <v>5579</v>
+        <v>5675</v>
       </c>
       <c r="D3" t="n">
-        <v>14539</v>
+        <v>14867</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3221</v>
+        <v>2208</v>
       </c>
       <c r="C4" t="n">
-        <v>6354</v>
+        <v>6592</v>
       </c>
       <c r="D4" t="n">
-        <v>6303</v>
+        <v>8242</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1735</v>
+        <v>1290</v>
       </c>
       <c r="C5" t="n">
-        <v>4898</v>
+        <v>4094</v>
       </c>
       <c r="D5" t="n">
-        <v>2159</v>
+        <v>3191</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>897</v>
+        <v>684</v>
       </c>
       <c r="C6" t="n">
-        <v>2476</v>
+        <v>2339</v>
       </c>
       <c r="D6" t="n">
-        <v>987</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>374</v>
+        <v>276</v>
       </c>
       <c r="C7" t="n">
-        <v>948</v>
+        <v>1105</v>
       </c>
       <c r="D7" t="n">
-        <v>597</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>309</v>
+        <v>448</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
         <v>297</v>
@@ -6493,10 +6493,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6504,7 +6504,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
         <v>149</v>
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>157</v>
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6580,7 +6580,7 @@
         <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_1_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_1_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4016</v>
+        <v>4655</v>
       </c>
       <c r="C2" t="n">
-        <v>11168</v>
+        <v>7587</v>
       </c>
       <c r="D2" t="n">
-        <v>33372</v>
+        <v>25951</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2860</v>
+        <v>2909</v>
       </c>
       <c r="C3" t="n">
-        <v>5594</v>
+        <v>5304</v>
       </c>
       <c r="D3" t="n">
-        <v>14602</v>
+        <v>14169</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2268</v>
+        <v>2321</v>
       </c>
       <c r="C4" t="n">
-        <v>5979</v>
+        <v>4894</v>
       </c>
       <c r="D4" t="n">
-        <v>9057</v>
+        <v>6576</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1500</v>
+        <v>1561</v>
       </c>
       <c r="C5" t="n">
-        <v>5255</v>
+        <v>3984</v>
       </c>
       <c r="D5" t="n">
-        <v>3966</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>879</v>
+        <v>956</v>
       </c>
       <c r="C6" t="n">
-        <v>3134</v>
+        <v>2220</v>
       </c>
       <c r="D6" t="n">
-        <v>1504</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>408</v>
+        <v>480</v>
       </c>
       <c r="C7" t="n">
-        <v>1697</v>
+        <v>1384</v>
       </c>
       <c r="D7" t="n">
-        <v>719</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="C8" t="n">
-        <v>746</v>
+        <v>791</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C9" t="n">
-        <v>332</v>
+        <v>376</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D11" t="n">
         <v>202</v>
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
         <v>161</v>
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5858</v>
+        <v>5254</v>
       </c>
       <c r="C2" t="n">
-        <v>9889</v>
+        <v>10479</v>
       </c>
       <c r="D2" t="n">
-        <v>29971</v>
+        <v>20282</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2754</v>
+        <v>3014</v>
       </c>
       <c r="C3" t="n">
-        <v>7116</v>
+        <v>5600</v>
       </c>
       <c r="D3" t="n">
-        <v>16173</v>
+        <v>14890</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2177</v>
+        <v>2212</v>
       </c>
       <c r="C4" t="n">
-        <v>5673</v>
+        <v>4996</v>
       </c>
       <c r="D4" t="n">
-        <v>9686</v>
+        <v>7688</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1612</v>
+        <v>1681</v>
       </c>
       <c r="C5" t="n">
-        <v>5421</v>
+        <v>4299</v>
       </c>
       <c r="D5" t="n">
-        <v>4589</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1038</v>
+        <v>1130</v>
       </c>
       <c r="C6" t="n">
-        <v>4040</v>
+        <v>3027</v>
       </c>
       <c r="D6" t="n">
-        <v>1862</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>541</v>
+        <v>619</v>
       </c>
       <c r="C7" t="n">
-        <v>2299</v>
+        <v>1754</v>
       </c>
       <c r="D7" t="n">
-        <v>820</v>
+        <v>701</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>229</v>
+        <v>275</v>
       </c>
       <c r="C8" t="n">
-        <v>1139</v>
+        <v>1058</v>
       </c>
       <c r="D8" t="n">
-        <v>473</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="C9" t="n">
-        <v>502</v>
+        <v>551</v>
       </c>
       <c r="D9" t="n">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6232</v>
+        <v>7231</v>
       </c>
       <c r="C2" t="n">
-        <v>11255</v>
+        <v>6935</v>
       </c>
       <c r="D2" t="n">
-        <v>31389</v>
+        <v>28273</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3212</v>
+        <v>3222</v>
       </c>
       <c r="C3" t="n">
-        <v>7385</v>
+        <v>6819</v>
       </c>
       <c r="D3" t="n">
-        <v>16793</v>
+        <v>14603</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2055</v>
+        <v>2176</v>
       </c>
       <c r="C4" t="n">
-        <v>6110</v>
+        <v>5170</v>
       </c>
       <c r="D4" t="n">
-        <v>10232</v>
+        <v>8486</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1635</v>
+        <v>1713</v>
       </c>
       <c r="C5" t="n">
-        <v>5360</v>
+        <v>4476</v>
       </c>
       <c r="D5" t="n">
-        <v>5183</v>
+        <v>3642</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1154</v>
+        <v>1242</v>
       </c>
       <c r="C6" t="n">
-        <v>4561</v>
+        <v>3518</v>
       </c>
       <c r="D6" t="n">
-        <v>2186</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>666</v>
+        <v>747</v>
       </c>
       <c r="C7" t="n">
-        <v>2958</v>
+        <v>2302</v>
       </c>
       <c r="D7" t="n">
-        <v>954</v>
+        <v>778</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>305</v>
+        <v>367</v>
       </c>
       <c r="C8" t="n">
-        <v>1570</v>
+        <v>1333</v>
       </c>
       <c r="D8" t="n">
-        <v>507</v>
+        <v>489</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="C9" t="n">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C10" t="n">
-        <v>339</v>
+        <v>383</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1542,10 +1542,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
         <v>164</v>
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5703</v>
+        <v>6452</v>
       </c>
       <c r="C2" t="n">
-        <v>7743</v>
+        <v>4604</v>
       </c>
       <c r="D2" t="n">
-        <v>25917</v>
+        <v>22952</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3775</v>
+        <v>3940</v>
       </c>
       <c r="C3" t="n">
-        <v>10872</v>
+        <v>9474</v>
       </c>
       <c r="D3" t="n">
-        <v>18458</v>
+        <v>16209</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1510</v>
+        <v>1582</v>
       </c>
       <c r="C4" t="n">
-        <v>8488</v>
+        <v>7274</v>
       </c>
       <c r="D4" t="n">
-        <v>10261</v>
+        <v>8103</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1066</v>
+        <v>1147</v>
       </c>
       <c r="C5" t="n">
-        <v>4469</v>
+        <v>3447</v>
       </c>
       <c r="D5" t="n">
-        <v>3535</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>615</v>
+        <v>690</v>
       </c>
       <c r="C6" t="n">
-        <v>2898</v>
+        <v>2255</v>
       </c>
       <c r="D6" t="n">
-        <v>934</v>
+        <v>762</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>281</v>
+        <v>339</v>
       </c>
       <c r="C7" t="n">
-        <v>1538</v>
+        <v>1306</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="C8" t="n">
-        <v>724</v>
+        <v>738</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>332</v>
+        <v>375</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
@@ -1839,10 +1839,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
         <v>160</v>
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>98</v>
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3416</v>
+        <v>3863</v>
       </c>
       <c r="C2" t="n">
-        <v>4325</v>
+        <v>2534</v>
       </c>
       <c r="D2" t="n">
-        <v>18261</v>
+        <v>16572</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3947</v>
+        <v>4316</v>
       </c>
       <c r="C3" t="n">
-        <v>8586</v>
+        <v>6499</v>
       </c>
       <c r="D3" t="n">
-        <v>18586</v>
+        <v>16376</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2071</v>
+        <v>2192</v>
       </c>
       <c r="C4" t="n">
-        <v>9735</v>
+        <v>8388</v>
       </c>
       <c r="D4" t="n">
-        <v>11227</v>
+        <v>9179</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1165</v>
+        <v>1264</v>
       </c>
       <c r="C5" t="n">
-        <v>6211</v>
+        <v>5194</v>
       </c>
       <c r="D5" t="n">
-        <v>4334</v>
+        <v>3234</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>727</v>
+        <v>827</v>
       </c>
       <c r="C6" t="n">
-        <v>3574</v>
+        <v>2826</v>
       </c>
       <c r="D6" t="n">
-        <v>1199</v>
+        <v>940</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>263</v>
+        <v>323</v>
       </c>
       <c r="C7" t="n">
-        <v>2032</v>
+        <v>1690</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="C8" t="n">
-        <v>955</v>
+        <v>939</v>
       </c>
       <c r="D8" t="n">
-        <v>336</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>376</v>
+        <v>439</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2136,10 +2136,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="D10" t="n">
         <v>210</v>
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2947</v>
+        <v>3465</v>
       </c>
       <c r="C2" t="n">
-        <v>3714</v>
+        <v>7196</v>
       </c>
       <c r="D2" t="n">
-        <v>14889</v>
+        <v>16886</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3131</v>
+        <v>3455</v>
       </c>
       <c r="C3" t="n">
-        <v>5885</v>
+        <v>4027</v>
       </c>
       <c r="D3" t="n">
-        <v>17292</v>
+        <v>15277</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2472</v>
+        <v>2701</v>
       </c>
       <c r="C4" t="n">
-        <v>8980</v>
+        <v>7252</v>
       </c>
       <c r="D4" t="n">
-        <v>12086</v>
+        <v>10143</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1370</v>
+        <v>1482</v>
       </c>
       <c r="C5" t="n">
-        <v>7705</v>
+        <v>6699</v>
       </c>
       <c r="D5" t="n">
-        <v>5261</v>
+        <v>4105</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>833</v>
+        <v>936</v>
       </c>
       <c r="C6" t="n">
-        <v>4739</v>
+        <v>3888</v>
       </c>
       <c r="D6" t="n">
-        <v>1634</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>389</v>
+        <v>468</v>
       </c>
       <c r="C7" t="n">
-        <v>2700</v>
+        <v>2217</v>
       </c>
       <c r="D7" t="n">
-        <v>635</v>
+        <v>575</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="C8" t="n">
-        <v>1376</v>
+        <v>1264</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C9" t="n">
-        <v>598</v>
+        <v>639</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>272</v>
+        <v>315</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
         <v>102</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1766</v>
+        <v>2021</v>
       </c>
       <c r="C2" t="n">
-        <v>1779</v>
+        <v>3246</v>
       </c>
       <c r="D2" t="n">
-        <v>10387</v>
+        <v>11671</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2980</v>
+        <v>3361</v>
       </c>
       <c r="C3" t="n">
-        <v>5003</v>
+        <v>5007</v>
       </c>
       <c r="D3" t="n">
-        <v>16654</v>
+        <v>15090</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2718</v>
+        <v>3002</v>
       </c>
       <c r="C4" t="n">
-        <v>8674</v>
+        <v>6682</v>
       </c>
       <c r="D4" t="n">
-        <v>12799</v>
+        <v>10814</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1438</v>
+        <v>1576</v>
       </c>
       <c r="C5" t="n">
-        <v>9115</v>
+        <v>7804</v>
       </c>
       <c r="D5" t="n">
-        <v>5524</v>
+        <v>4455</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>690</v>
+        <v>830</v>
       </c>
       <c r="C6" t="n">
-        <v>5608</v>
+        <v>4781</v>
       </c>
       <c r="D6" t="n">
-        <v>1580</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="C7" t="n">
-        <v>2703</v>
+        <v>2329</v>
       </c>
       <c r="D7" t="n">
-        <v>621</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>1004</v>
+        <v>1034</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2590</v>
+        <v>2874</v>
       </c>
       <c r="C2" t="n">
-        <v>5489</v>
+        <v>5706</v>
       </c>
       <c r="D2" t="n">
-        <v>15130</v>
+        <v>9896</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2139</v>
+        <v>2384</v>
       </c>
       <c r="C3" t="n">
-        <v>3194</v>
+        <v>3705</v>
       </c>
       <c r="D3" t="n">
-        <v>14842</v>
+        <v>13704</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2470</v>
+        <v>2785</v>
       </c>
       <c r="C4" t="n">
-        <v>6801</v>
+        <v>5787</v>
       </c>
       <c r="D4" t="n">
-        <v>13002</v>
+        <v>11183</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1727</v>
+        <v>1922</v>
       </c>
       <c r="C5" t="n">
-        <v>8818</v>
+        <v>7124</v>
       </c>
       <c r="D5" t="n">
-        <v>6403</v>
+        <v>5296</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>883</v>
+        <v>1032</v>
       </c>
       <c r="C6" t="n">
-        <v>7060</v>
+        <v>6163</v>
       </c>
       <c r="D6" t="n">
-        <v>2089</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>255</v>
+        <v>326</v>
       </c>
       <c r="C7" t="n">
-        <v>3893</v>
+        <v>3360</v>
       </c>
       <c r="D7" t="n">
-        <v>742</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>1622</v>
+        <v>1558</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>505</v>
+        <v>558</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1675</v>
+        <v>1969</v>
       </c>
       <c r="C2" t="n">
-        <v>3095</v>
+        <v>2966</v>
       </c>
       <c r="D2" t="n">
-        <v>11413</v>
+        <v>7519</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1998</v>
+        <v>2231</v>
       </c>
       <c r="C3" t="n">
-        <v>3741</v>
+        <v>4137</v>
       </c>
       <c r="D3" t="n">
-        <v>14211</v>
+        <v>12580</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2169</v>
+        <v>2453</v>
       </c>
       <c r="C4" t="n">
-        <v>5370</v>
+        <v>4953</v>
       </c>
       <c r="D4" t="n">
-        <v>12961</v>
+        <v>11289</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1867</v>
+        <v>2096</v>
       </c>
       <c r="C5" t="n">
-        <v>8256</v>
+        <v>6680</v>
       </c>
       <c r="D5" t="n">
-        <v>6966</v>
+        <v>5914</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1028</v>
+        <v>1204</v>
       </c>
       <c r="C6" t="n">
-        <v>7882</v>
+        <v>6734</v>
       </c>
       <c r="D6" t="n">
-        <v>2498</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>229</v>
+        <v>316</v>
       </c>
       <c r="C7" t="n">
-        <v>4903</v>
+        <v>4330</v>
       </c>
       <c r="D7" t="n">
-        <v>834</v>
+        <v>744</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>2122</v>
+        <v>2044</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>580</v>
+        <v>667</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2096</v>
+        <v>3290</v>
       </c>
       <c r="C2" t="n">
-        <v>6956</v>
+        <v>6564</v>
       </c>
       <c r="D2" t="n">
-        <v>13435</v>
+        <v>14582</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1588</v>
+        <v>1796</v>
       </c>
       <c r="C3" t="n">
-        <v>3136</v>
+        <v>3259</v>
       </c>
       <c r="D3" t="n">
-        <v>12965</v>
+        <v>11106</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1833</v>
+        <v>2061</v>
       </c>
       <c r="C4" t="n">
-        <v>4585</v>
+        <v>4489</v>
       </c>
       <c r="D4" t="n">
-        <v>12746</v>
+        <v>11144</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1817</v>
+        <v>2029</v>
       </c>
       <c r="C5" t="n">
-        <v>6948</v>
+        <v>5811</v>
       </c>
       <c r="D5" t="n">
-        <v>7559</v>
+        <v>6508</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1201</v>
+        <v>1417</v>
       </c>
       <c r="C6" t="n">
-        <v>7957</v>
+        <v>6652</v>
       </c>
       <c r="D6" t="n">
-        <v>3023</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>426</v>
+        <v>546</v>
       </c>
       <c r="C7" t="n">
-        <v>5981</v>
+        <v>5313</v>
       </c>
       <c r="D7" t="n">
-        <v>1021</v>
+        <v>901</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="C8" t="n">
-        <v>3095</v>
+        <v>2872</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>1063</v>
+        <v>1145</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>323</v>
+        <v>376</v>
       </c>
       <c r="D10" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4475</v>
+        <v>4961</v>
       </c>
       <c r="C2" t="n">
-        <v>5577</v>
+        <v>7069</v>
       </c>
       <c r="D2" t="n">
-        <v>23010</v>
+        <v>8748</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1515</v>
+        <v>2327</v>
       </c>
       <c r="C2" t="n">
-        <v>4006</v>
+        <v>3675</v>
       </c>
       <c r="D2" t="n">
-        <v>9995</v>
+        <v>10732</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2114</v>
+        <v>2478</v>
       </c>
       <c r="C3" t="n">
-        <v>4267</v>
+        <v>4328</v>
       </c>
       <c r="D3" t="n">
-        <v>14055</v>
+        <v>12236</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2613</v>
+        <v>2923</v>
       </c>
       <c r="C4" t="n">
-        <v>6903</v>
+        <v>6414</v>
       </c>
       <c r="D4" t="n">
-        <v>13193</v>
+        <v>11555</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1143</v>
+        <v>1384</v>
       </c>
       <c r="C5" t="n">
-        <v>10785</v>
+        <v>8933</v>
       </c>
       <c r="D5" t="n">
-        <v>6923</v>
+        <v>5989</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>393</v>
+        <v>504</v>
       </c>
       <c r="C6" t="n">
-        <v>7342</v>
+        <v>6640</v>
       </c>
       <c r="D6" t="n">
-        <v>2351</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>3033</v>
+        <v>2814</v>
       </c>
       <c r="D7" t="n">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>1041</v>
+        <v>1122</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>316</v>
+        <v>368</v>
       </c>
       <c r="D9" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5874</v>
+        <v>7070</v>
       </c>
       <c r="C2" t="n">
-        <v>5688</v>
+        <v>3858</v>
       </c>
       <c r="D2" t="n">
-        <v>34167</v>
+        <v>11153</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1903</v>
+        <v>2109</v>
       </c>
       <c r="C3" t="n">
-        <v>2810</v>
+        <v>3562</v>
       </c>
       <c r="D3" t="n">
-        <v>4505</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5021</v>
+        <v>4403</v>
       </c>
       <c r="C2" t="n">
-        <v>6855</v>
+        <v>3565</v>
       </c>
       <c r="D2" t="n">
-        <v>32816</v>
+        <v>14818</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3191</v>
+        <v>3765</v>
       </c>
       <c r="C3" t="n">
-        <v>3827</v>
+        <v>3212</v>
       </c>
       <c r="D3" t="n">
-        <v>9156</v>
+        <v>3472</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>861</v>
+        <v>950</v>
       </c>
       <c r="C4" t="n">
-        <v>1691</v>
+        <v>2163</v>
       </c>
       <c r="D4" t="n">
-        <v>2089</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4269</v>
+        <v>4188</v>
       </c>
       <c r="C2" t="n">
-        <v>8037</v>
+        <v>3090</v>
       </c>
       <c r="D2" t="n">
-        <v>29029</v>
+        <v>17659</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3354</v>
+        <v>3361</v>
       </c>
       <c r="C3" t="n">
-        <v>4723</v>
+        <v>2946</v>
       </c>
       <c r="D3" t="n">
-        <v>12282</v>
+        <v>5037</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1720</v>
+        <v>1992</v>
       </c>
       <c r="C4" t="n">
-        <v>2828</v>
+        <v>2691</v>
       </c>
       <c r="D4" t="n">
-        <v>3382</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>407</v>
+        <v>450</v>
       </c>
       <c r="C5" t="n">
-        <v>1022</v>
+        <v>1297</v>
       </c>
       <c r="D5" t="n">
-        <v>1312</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4326</v>
+        <v>4500</v>
       </c>
       <c r="C2" t="n">
-        <v>9604</v>
+        <v>7467</v>
       </c>
       <c r="D2" t="n">
-        <v>22561</v>
+        <v>26897</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3114</v>
+        <v>3092</v>
       </c>
       <c r="C3" t="n">
-        <v>5576</v>
+        <v>2625</v>
       </c>
       <c r="D3" t="n">
-        <v>13962</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2120</v>
+        <v>2262</v>
       </c>
       <c r="C4" t="n">
-        <v>3742</v>
+        <v>2774</v>
       </c>
       <c r="D4" t="n">
-        <v>4902</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>873</v>
+        <v>1013</v>
       </c>
       <c r="C5" t="n">
-        <v>1936</v>
+        <v>2006</v>
       </c>
       <c r="D5" t="n">
-        <v>1617</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="C6" t="n">
-        <v>660</v>
+        <v>802</v>
       </c>
       <c r="D6" t="n">
-        <v>965</v>
+        <v>941</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5330</v>
+        <v>4873</v>
       </c>
       <c r="C2" t="n">
-        <v>11244</v>
+        <v>9922</v>
       </c>
       <c r="D2" t="n">
-        <v>27385</v>
+        <v>30016</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2695</v>
+        <v>2761</v>
       </c>
       <c r="C3" t="n">
-        <v>6225</v>
+        <v>4213</v>
       </c>
       <c r="D3" t="n">
-        <v>13442</v>
+        <v>8673</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1625</v>
+        <v>1661</v>
       </c>
       <c r="C4" t="n">
-        <v>3845</v>
+        <v>2206</v>
       </c>
       <c r="D4" t="n">
-        <v>5588</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>769</v>
+        <v>866</v>
       </c>
       <c r="C5" t="n">
-        <v>2099</v>
+        <v>1747</v>
       </c>
       <c r="D5" t="n">
-        <v>1716</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>261</v>
+        <v>302</v>
       </c>
       <c r="C6" t="n">
-        <v>864</v>
+        <v>957</v>
       </c>
       <c r="D6" t="n">
-        <v>819</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>321</v>
+        <v>367</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4299</v>
+        <v>4552</v>
       </c>
       <c r="C2" t="n">
-        <v>5335</v>
+        <v>5061</v>
       </c>
       <c r="D2" t="n">
-        <v>21908</v>
+        <v>25873</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3319</v>
+        <v>3187</v>
       </c>
       <c r="C3" t="n">
-        <v>7937</v>
+        <v>6575</v>
       </c>
       <c r="D3" t="n">
-        <v>14795</v>
+        <v>11777</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1886</v>
+        <v>1949</v>
       </c>
       <c r="C4" t="n">
-        <v>5144</v>
+        <v>3412</v>
       </c>
       <c r="D4" t="n">
-        <v>6947</v>
+        <v>3866</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1054</v>
+        <v>1127</v>
       </c>
       <c r="C5" t="n">
-        <v>3077</v>
+        <v>1988</v>
       </c>
       <c r="D5" t="n">
-        <v>2444</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>475</v>
+        <v>550</v>
       </c>
       <c r="C6" t="n">
-        <v>1552</v>
+        <v>1407</v>
       </c>
       <c r="D6" t="n">
-        <v>979</v>
+        <v>832</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="C7" t="n">
-        <v>624</v>
+        <v>707</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>274</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3882</v>
+        <v>3910</v>
       </c>
       <c r="C2" t="n">
-        <v>7150</v>
+        <v>7191</v>
       </c>
       <c r="D2" t="n">
-        <v>20136</v>
+        <v>25295</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3121</v>
+        <v>3187</v>
       </c>
       <c r="C3" t="n">
-        <v>5675</v>
+        <v>4931</v>
       </c>
       <c r="D3" t="n">
-        <v>14867</v>
+        <v>13278</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2208</v>
+        <v>2231</v>
       </c>
       <c r="C4" t="n">
-        <v>6592</v>
+        <v>5193</v>
       </c>
       <c r="D4" t="n">
-        <v>8242</v>
+        <v>5343</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1290</v>
+        <v>1365</v>
       </c>
       <c r="C5" t="n">
-        <v>4094</v>
+        <v>2753</v>
       </c>
       <c r="D5" t="n">
-        <v>3191</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>684</v>
+        <v>763</v>
       </c>
       <c r="C6" t="n">
-        <v>2339</v>
+        <v>1708</v>
       </c>
       <c r="D6" t="n">
-        <v>1209</v>
+        <v>923</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="C7" t="n">
-        <v>1105</v>
+        <v>1084</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>448</v>
+        <v>510</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6633,10 +6633,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_1_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_1_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4655</v>
+        <v>1228</v>
       </c>
       <c r="C2" t="n">
-        <v>7587</v>
+        <v>2066</v>
       </c>
       <c r="D2" t="n">
-        <v>25951</v>
+        <v>15282</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2909</v>
+        <v>2072</v>
       </c>
       <c r="C3" t="n">
-        <v>5304</v>
+        <v>5853</v>
       </c>
       <c r="D3" t="n">
-        <v>14169</v>
+        <v>12051</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2321</v>
+        <v>1379</v>
       </c>
       <c r="C4" t="n">
-        <v>4894</v>
+        <v>7767</v>
       </c>
       <c r="D4" t="n">
-        <v>6576</v>
+        <v>5401</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1561</v>
+        <v>737</v>
       </c>
       <c r="C5" t="n">
-        <v>3984</v>
+        <v>5214</v>
       </c>
       <c r="D5" t="n">
-        <v>2440</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>956</v>
+        <v>304</v>
       </c>
       <c r="C6" t="n">
-        <v>2220</v>
+        <v>2052</v>
       </c>
       <c r="D6" t="n">
-        <v>1072</v>
+        <v>748</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>480</v>
+        <v>104</v>
       </c>
       <c r="C7" t="n">
-        <v>1384</v>
+        <v>748</v>
       </c>
       <c r="D7" t="n">
-        <v>648</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>183</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>791</v>
+        <v>352</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>376</v>
+        <v>283</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5254</v>
+        <v>1083</v>
       </c>
       <c r="C2" t="n">
-        <v>10479</v>
+        <v>7911</v>
       </c>
       <c r="D2" t="n">
-        <v>20282</v>
+        <v>15483</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3014</v>
+        <v>1424</v>
       </c>
       <c r="C3" t="n">
-        <v>5600</v>
+        <v>3374</v>
       </c>
       <c r="D3" t="n">
-        <v>14890</v>
+        <v>11815</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2212</v>
+        <v>1470</v>
       </c>
       <c r="C4" t="n">
-        <v>4996</v>
+        <v>6558</v>
       </c>
       <c r="D4" t="n">
-        <v>7688</v>
+        <v>6449</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1681</v>
+        <v>925</v>
       </c>
       <c r="C5" t="n">
-        <v>4299</v>
+        <v>6503</v>
       </c>
       <c r="D5" t="n">
-        <v>3017</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1130</v>
+        <v>449</v>
       </c>
       <c r="C6" t="n">
-        <v>3027</v>
+        <v>3628</v>
       </c>
       <c r="D6" t="n">
-        <v>1280</v>
+        <v>931</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>619</v>
+        <v>168</v>
       </c>
       <c r="C7" t="n">
-        <v>1754</v>
+        <v>1381</v>
       </c>
       <c r="D7" t="n">
-        <v>701</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>275</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>1058</v>
+        <v>533</v>
       </c>
       <c r="D8" t="n">
-        <v>467</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>551</v>
+        <v>317</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>285</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7231</v>
+        <v>575</v>
       </c>
       <c r="C2" t="n">
-        <v>6935</v>
+        <v>3256</v>
       </c>
       <c r="D2" t="n">
-        <v>28273</v>
+        <v>10417</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3222</v>
+        <v>1277</v>
       </c>
       <c r="C3" t="n">
-        <v>6819</v>
+        <v>5012</v>
       </c>
       <c r="D3" t="n">
-        <v>14603</v>
+        <v>11963</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2176</v>
+        <v>1611</v>
       </c>
       <c r="C4" t="n">
-        <v>5170</v>
+        <v>5860</v>
       </c>
       <c r="D4" t="n">
-        <v>8486</v>
+        <v>7242</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1713</v>
+        <v>938</v>
       </c>
       <c r="C5" t="n">
-        <v>4476</v>
+        <v>7256</v>
       </c>
       <c r="D5" t="n">
-        <v>3642</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1242</v>
+        <v>358</v>
       </c>
       <c r="C6" t="n">
-        <v>3518</v>
+        <v>4669</v>
       </c>
       <c r="D6" t="n">
-        <v>1500</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>747</v>
+        <v>73</v>
       </c>
       <c r="C7" t="n">
-        <v>2302</v>
+        <v>1322</v>
       </c>
       <c r="D7" t="n">
-        <v>778</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>367</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1333</v>
+        <v>498</v>
       </c>
       <c r="D8" t="n">
-        <v>489</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>151</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>754</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
-        <v>340</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>383</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6452</v>
+        <v>693</v>
       </c>
       <c r="C2" t="n">
-        <v>4604</v>
+        <v>2940</v>
       </c>
       <c r="D2" t="n">
-        <v>22952</v>
+        <v>11429</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3940</v>
+        <v>820</v>
       </c>
       <c r="C3" t="n">
-        <v>9474</v>
+        <v>3623</v>
       </c>
       <c r="D3" t="n">
-        <v>16209</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1582</v>
+        <v>1302</v>
       </c>
       <c r="C4" t="n">
-        <v>7274</v>
+        <v>5346</v>
       </c>
       <c r="D4" t="n">
-        <v>8103</v>
+        <v>7837</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1147</v>
+        <v>1103</v>
       </c>
       <c r="C5" t="n">
-        <v>3447</v>
+        <v>6477</v>
       </c>
       <c r="D5" t="n">
-        <v>2483</v>
+        <v>3413</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>690</v>
+        <v>540</v>
       </c>
       <c r="C6" t="n">
-        <v>2255</v>
+        <v>5884</v>
       </c>
       <c r="D6" t="n">
-        <v>762</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>339</v>
+        <v>153</v>
       </c>
       <c r="C7" t="n">
-        <v>1306</v>
+        <v>2856</v>
       </c>
       <c r="D7" t="n">
-        <v>479</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>139</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>738</v>
+        <v>851</v>
       </c>
       <c r="D8" t="n">
-        <v>333</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>375</v>
+        <v>339</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3863</v>
+        <v>384</v>
       </c>
       <c r="C2" t="n">
-        <v>2534</v>
+        <v>2118</v>
       </c>
       <c r="D2" t="n">
-        <v>16572</v>
+        <v>8298</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4316</v>
+        <v>674</v>
       </c>
       <c r="C3" t="n">
-        <v>6499</v>
+        <v>2973</v>
       </c>
       <c r="D3" t="n">
-        <v>16376</v>
+        <v>10424</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2192</v>
+        <v>1050</v>
       </c>
       <c r="C4" t="n">
-        <v>8388</v>
+        <v>4578</v>
       </c>
       <c r="D4" t="n">
-        <v>9179</v>
+        <v>8159</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1264</v>
+        <v>1146</v>
       </c>
       <c r="C5" t="n">
-        <v>5194</v>
+        <v>6113</v>
       </c>
       <c r="D5" t="n">
-        <v>3234</v>
+        <v>3969</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>827</v>
+        <v>663</v>
       </c>
       <c r="C6" t="n">
-        <v>2826</v>
+        <v>6399</v>
       </c>
       <c r="D6" t="n">
-        <v>940</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>323</v>
+        <v>172</v>
       </c>
       <c r="C7" t="n">
-        <v>1690</v>
+        <v>3941</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>665</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>939</v>
+        <v>1338</v>
       </c>
       <c r="D8" t="n">
-        <v>348</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3465</v>
+        <v>653</v>
       </c>
       <c r="C2" t="n">
-        <v>7196</v>
+        <v>17754</v>
       </c>
       <c r="D2" t="n">
-        <v>16886</v>
+        <v>17088</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3455</v>
+        <v>467</v>
       </c>
       <c r="C3" t="n">
-        <v>4027</v>
+        <v>2262</v>
       </c>
       <c r="D3" t="n">
-        <v>15277</v>
+        <v>9434</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2701</v>
+        <v>781</v>
       </c>
       <c r="C4" t="n">
-        <v>7252</v>
+        <v>3740</v>
       </c>
       <c r="D4" t="n">
-        <v>10143</v>
+        <v>8280</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1482</v>
+        <v>1026</v>
       </c>
       <c r="C5" t="n">
-        <v>6699</v>
+        <v>5278</v>
       </c>
       <c r="D5" t="n">
-        <v>4105</v>
+        <v>4491</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>936</v>
+        <v>791</v>
       </c>
       <c r="C6" t="n">
-        <v>3888</v>
+        <v>6211</v>
       </c>
       <c r="D6" t="n">
-        <v>1279</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>468</v>
+        <v>313</v>
       </c>
       <c r="C7" t="n">
-        <v>2217</v>
+        <v>5037</v>
       </c>
       <c r="D7" t="n">
-        <v>575</v>
+        <v>767</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>170</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>1264</v>
+        <v>2396</v>
       </c>
       <c r="D8" t="n">
-        <v>367</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>639</v>
+        <v>786</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
         <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2021</v>
+        <v>438</v>
       </c>
       <c r="C2" t="n">
-        <v>3246</v>
+        <v>9233</v>
       </c>
       <c r="D2" t="n">
-        <v>11671</v>
+        <v>12303</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3361</v>
+        <v>701</v>
       </c>
       <c r="C3" t="n">
-        <v>5007</v>
+        <v>6773</v>
       </c>
       <c r="D3" t="n">
-        <v>15090</v>
+        <v>10821</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3002</v>
+        <v>1327</v>
       </c>
       <c r="C4" t="n">
-        <v>6682</v>
+        <v>5327</v>
       </c>
       <c r="D4" t="n">
-        <v>10814</v>
+        <v>8542</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1576</v>
+        <v>797</v>
       </c>
       <c r="C5" t="n">
-        <v>7804</v>
+        <v>8263</v>
       </c>
       <c r="D5" t="n">
-        <v>4455</v>
+        <v>4169</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>830</v>
+        <v>289</v>
       </c>
       <c r="C6" t="n">
-        <v>4781</v>
+        <v>6457</v>
       </c>
       <c r="D6" t="n">
-        <v>1263</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>157</v>
+        <v>76</v>
       </c>
       <c r="C7" t="n">
-        <v>2329</v>
+        <v>2348</v>
       </c>
       <c r="D7" t="n">
-        <v>582</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>1034</v>
+        <v>770</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2874</v>
+        <v>214</v>
       </c>
       <c r="C2" t="n">
-        <v>5706</v>
+        <v>3970</v>
       </c>
       <c r="D2" t="n">
-        <v>9896</v>
+        <v>9089</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2384</v>
+        <v>498</v>
       </c>
       <c r="C3" t="n">
-        <v>3705</v>
+        <v>7027</v>
       </c>
       <c r="D3" t="n">
-        <v>13704</v>
+        <v>10258</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2785</v>
+        <v>871</v>
       </c>
       <c r="C4" t="n">
-        <v>5787</v>
+        <v>5759</v>
       </c>
       <c r="D4" t="n">
-        <v>11183</v>
+        <v>8316</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1922</v>
+        <v>734</v>
       </c>
       <c r="C5" t="n">
-        <v>7124</v>
+        <v>6047</v>
       </c>
       <c r="D5" t="n">
-        <v>5296</v>
+        <v>4320</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1032</v>
+        <v>286</v>
       </c>
       <c r="C6" t="n">
-        <v>6163</v>
+        <v>6018</v>
       </c>
       <c r="D6" t="n">
-        <v>1718</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>326</v>
+        <v>66</v>
       </c>
       <c r="C7" t="n">
-        <v>3360</v>
+        <v>2972</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1558</v>
+        <v>895</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>558</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>131</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1969</v>
+        <v>373</v>
       </c>
       <c r="C2" t="n">
-        <v>2966</v>
+        <v>6073</v>
       </c>
       <c r="D2" t="n">
-        <v>7519</v>
+        <v>7406</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2231</v>
+        <v>304</v>
       </c>
       <c r="C3" t="n">
-        <v>4137</v>
+        <v>4707</v>
       </c>
       <c r="D3" t="n">
-        <v>12580</v>
+        <v>9332</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2453</v>
+        <v>611</v>
       </c>
       <c r="C4" t="n">
-        <v>4953</v>
+        <v>6345</v>
       </c>
       <c r="D4" t="n">
-        <v>11289</v>
+        <v>8436</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2096</v>
+        <v>727</v>
       </c>
       <c r="C5" t="n">
-        <v>6680</v>
+        <v>5824</v>
       </c>
       <c r="D5" t="n">
-        <v>5914</v>
+        <v>4917</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1204</v>
+        <v>446</v>
       </c>
       <c r="C6" t="n">
-        <v>6734</v>
+        <v>5966</v>
       </c>
       <c r="D6" t="n">
-        <v>2040</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="7">
@@ -3338,10 +3338,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>316</v>
+        <v>142</v>
       </c>
       <c r="C7" t="n">
-        <v>4330</v>
+        <v>4522</v>
       </c>
       <c r="D7" t="n">
         <v>744</v>
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>2044</v>
+        <v>1880</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>667</v>
+        <v>557</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>241</v>
+        <v>196</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3290</v>
+        <v>962</v>
       </c>
       <c r="C2" t="n">
-        <v>6564</v>
+        <v>15403</v>
       </c>
       <c r="D2" t="n">
-        <v>14582</v>
+        <v>13882</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1796</v>
+        <v>276</v>
       </c>
       <c r="C3" t="n">
-        <v>3259</v>
+        <v>4698</v>
       </c>
       <c r="D3" t="n">
-        <v>11106</v>
+        <v>8412</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2061</v>
+        <v>415</v>
       </c>
       <c r="C4" t="n">
-        <v>4489</v>
+        <v>5379</v>
       </c>
       <c r="D4" t="n">
-        <v>11144</v>
+        <v>8334</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2029</v>
+        <v>614</v>
       </c>
       <c r="C5" t="n">
-        <v>5811</v>
+        <v>5902</v>
       </c>
       <c r="D5" t="n">
-        <v>6508</v>
+        <v>5294</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1417</v>
+        <v>526</v>
       </c>
       <c r="C6" t="n">
-        <v>6652</v>
+        <v>5835</v>
       </c>
       <c r="D6" t="n">
-        <v>2534</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>546</v>
+        <v>243</v>
       </c>
       <c r="C7" t="n">
-        <v>5313</v>
+        <v>5199</v>
       </c>
       <c r="D7" t="n">
-        <v>901</v>
+        <v>943</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>2872</v>
+        <v>3070</v>
       </c>
       <c r="D8" t="n">
-        <v>465</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>1145</v>
+        <v>1127</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>376</v>
+        <v>344</v>
       </c>
       <c r="D10" t="n">
-        <v>192</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4961</v>
+        <v>4844</v>
       </c>
       <c r="C2" t="n">
-        <v>7069</v>
+        <v>10637</v>
       </c>
       <c r="D2" t="n">
-        <v>8748</v>
+        <v>13830</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2327</v>
+        <v>1230</v>
       </c>
       <c r="C2" t="n">
-        <v>3675</v>
+        <v>9296</v>
       </c>
       <c r="D2" t="n">
-        <v>10732</v>
+        <v>17729</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2478</v>
+        <v>448</v>
       </c>
       <c r="C3" t="n">
-        <v>4328</v>
+        <v>8259</v>
       </c>
       <c r="D3" t="n">
-        <v>12236</v>
+        <v>8560</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2923</v>
+        <v>313</v>
       </c>
       <c r="C4" t="n">
-        <v>6414</v>
+        <v>4953</v>
       </c>
       <c r="D4" t="n">
-        <v>11555</v>
+        <v>8012</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1384</v>
+        <v>491</v>
       </c>
       <c r="C5" t="n">
-        <v>8933</v>
+        <v>5491</v>
       </c>
       <c r="D5" t="n">
-        <v>5989</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="C6" t="n">
-        <v>6640</v>
+        <v>5809</v>
       </c>
       <c r="D6" t="n">
-        <v>2001</v>
+        <v>2847</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>113</v>
+        <v>318</v>
       </c>
       <c r="C7" t="n">
-        <v>2814</v>
+        <v>5464</v>
       </c>
       <c r="D7" t="n">
-        <v>579</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="C8" t="n">
-        <v>1122</v>
+        <v>3894</v>
       </c>
       <c r="D8" t="n">
-        <v>302</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>368</v>
+        <v>1888</v>
       </c>
       <c r="D9" t="n">
-        <v>188</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>166</v>
+        <v>632</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>97</v>
+        <v>211</v>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7070</v>
+        <v>5238</v>
       </c>
       <c r="C2" t="n">
-        <v>3858</v>
+        <v>9933</v>
       </c>
       <c r="D2" t="n">
-        <v>11153</v>
+        <v>16992</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2109</v>
+        <v>1562</v>
       </c>
       <c r="C3" t="n">
-        <v>3562</v>
+        <v>4200</v>
       </c>
       <c r="D3" t="n">
-        <v>2108</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4403</v>
+        <v>2979</v>
       </c>
       <c r="C2" t="n">
-        <v>3565</v>
+        <v>6467</v>
       </c>
       <c r="D2" t="n">
-        <v>14818</v>
+        <v>19073</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3765</v>
+        <v>2874</v>
       </c>
       <c r="C3" t="n">
-        <v>3212</v>
+        <v>6576</v>
       </c>
       <c r="D3" t="n">
-        <v>3472</v>
+        <v>4861</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>950</v>
+        <v>748</v>
       </c>
       <c r="C4" t="n">
-        <v>2163</v>
+        <v>2668</v>
       </c>
       <c r="D4" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4188</v>
+        <v>2374</v>
       </c>
       <c r="C2" t="n">
-        <v>3090</v>
+        <v>7160</v>
       </c>
       <c r="D2" t="n">
-        <v>17659</v>
+        <v>17824</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3361</v>
+        <v>2414</v>
       </c>
       <c r="C3" t="n">
-        <v>2946</v>
+        <v>5606</v>
       </c>
       <c r="D3" t="n">
-        <v>5037</v>
+        <v>6890</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1992</v>
+        <v>1591</v>
       </c>
       <c r="C4" t="n">
-        <v>2691</v>
+        <v>4938</v>
       </c>
       <c r="D4" t="n">
-        <v>1915</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>450</v>
+        <v>366</v>
       </c>
       <c r="C5" t="n">
-        <v>1297</v>
+        <v>1621</v>
       </c>
       <c r="D5" t="n">
-        <v>1215</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4500</v>
+        <v>1535</v>
       </c>
       <c r="C2" t="n">
-        <v>7467</v>
+        <v>4679</v>
       </c>
       <c r="D2" t="n">
-        <v>26897</v>
+        <v>18054</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3092</v>
+        <v>1979</v>
       </c>
       <c r="C3" t="n">
-        <v>2625</v>
+        <v>5586</v>
       </c>
       <c r="D3" t="n">
-        <v>6600</v>
+        <v>8143</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2262</v>
+        <v>1712</v>
       </c>
       <c r="C4" t="n">
-        <v>2774</v>
+        <v>5213</v>
       </c>
       <c r="D4" t="n">
-        <v>2407</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1013</v>
+        <v>833</v>
       </c>
       <c r="C5" t="n">
-        <v>2006</v>
+        <v>3402</v>
       </c>
       <c r="D5" t="n">
-        <v>1305</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>260</v>
+        <v>213</v>
       </c>
       <c r="C6" t="n">
-        <v>802</v>
+        <v>977</v>
       </c>
       <c r="D6" t="n">
-        <v>941</v>
+        <v>841</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4873</v>
+        <v>2564</v>
       </c>
       <c r="C2" t="n">
-        <v>9922</v>
+        <v>7105</v>
       </c>
       <c r="D2" t="n">
-        <v>30016</v>
+        <v>17610</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2761</v>
+        <v>1470</v>
       </c>
       <c r="C3" t="n">
-        <v>4213</v>
+        <v>4455</v>
       </c>
       <c r="D3" t="n">
-        <v>8673</v>
+        <v>9076</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1661</v>
+        <v>1594</v>
       </c>
       <c r="C4" t="n">
-        <v>2206</v>
+        <v>5305</v>
       </c>
       <c r="D4" t="n">
-        <v>2683</v>
+        <v>3889</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>866</v>
+        <v>1095</v>
       </c>
       <c r="C5" t="n">
-        <v>1747</v>
+        <v>4270</v>
       </c>
       <c r="D5" t="n">
-        <v>1188</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>302</v>
+        <v>445</v>
       </c>
       <c r="C6" t="n">
-        <v>957</v>
+        <v>2177</v>
       </c>
       <c r="D6" t="n">
-        <v>756</v>
+        <v>904</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="C7" t="n">
-        <v>367</v>
+        <v>626</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>225</v>
+        <v>299</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4552</v>
+        <v>2821</v>
       </c>
       <c r="C2" t="n">
-        <v>5061</v>
+        <v>8236</v>
       </c>
       <c r="D2" t="n">
-        <v>25873</v>
+        <v>27231</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3187</v>
+        <v>1603</v>
       </c>
       <c r="C3" t="n">
-        <v>6575</v>
+        <v>5022</v>
       </c>
       <c r="D3" t="n">
-        <v>11777</v>
+        <v>9680</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1949</v>
+        <v>1338</v>
       </c>
       <c r="C4" t="n">
-        <v>3412</v>
+        <v>4762</v>
       </c>
       <c r="D4" t="n">
-        <v>3866</v>
+        <v>4667</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1127</v>
+        <v>1167</v>
       </c>
       <c r="C5" t="n">
-        <v>1988</v>
+        <v>4687</v>
       </c>
       <c r="D5" t="n">
-        <v>1441</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>550</v>
+        <v>665</v>
       </c>
       <c r="C6" t="n">
-        <v>1407</v>
+        <v>3139</v>
       </c>
       <c r="D6" t="n">
-        <v>832</v>
+        <v>993</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="C7" t="n">
-        <v>707</v>
+        <v>1334</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>446</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>213</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>238</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3910</v>
+        <v>2516</v>
       </c>
       <c r="C2" t="n">
-        <v>7191</v>
+        <v>5073</v>
       </c>
       <c r="D2" t="n">
-        <v>25295</v>
+        <v>21317</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3187</v>
+        <v>2246</v>
       </c>
       <c r="C3" t="n">
-        <v>4931</v>
+        <v>7936</v>
       </c>
       <c r="D3" t="n">
-        <v>13278</v>
+        <v>11059</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2231</v>
+        <v>1078</v>
       </c>
       <c r="C4" t="n">
-        <v>5193</v>
+        <v>7471</v>
       </c>
       <c r="D4" t="n">
-        <v>5343</v>
+        <v>4408</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1365</v>
+        <v>614</v>
       </c>
       <c r="C5" t="n">
-        <v>2753</v>
+        <v>3076</v>
       </c>
       <c r="D5" t="n">
-        <v>1862</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>763</v>
+        <v>222</v>
       </c>
       <c r="C6" t="n">
-        <v>1708</v>
+        <v>1307</v>
       </c>
       <c r="D6" t="n">
-        <v>923</v>
+        <v>645</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>326</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>1084</v>
+        <v>437</v>
       </c>
       <c r="D7" t="n">
-        <v>608</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>510</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>40</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
